--- a/Files/upload file.xlsx
+++ b/Files/upload file.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0 Hansoll AI\Design Terminology Organization\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EBB67CE-75C4-4346-952D-E47BE5C245E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77C8AEA1-9B35-4926-AD42-2DD616596A69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="14235" xr2:uid="{DCA174AC-C2FF-452A-B0BB-597EA014E074}"/>
+    <workbookView xWindow="4305" yWindow="840" windowWidth="21600" windowHeight="14235" xr2:uid="{DCA174AC-C2FF-452A-B0BB-597EA014E074}"/>
   </bookViews>
   <sheets>
     <sheet name="INDEX LIST" sheetId="6" r:id="rId1"/>
-    <sheet name="Image" sheetId="7" r:id="rId2"/>
-    <sheet name="DATABASE" sheetId="4" state="hidden" r:id="rId3"/>
-    <sheet name="LISTS" sheetId="5" state="hidden" r:id="rId4"/>
+    <sheet name="DATABASE" sheetId="4" state="hidden" r:id="rId2"/>
+    <sheet name="LISTS" sheetId="5" state="hidden" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029" forceFullCalc="1"/>
   <extLst>
@@ -707,7 +706,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -771,12 +770,6 @@
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
@@ -918,247 +911,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>194310</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00031C03-B742-42ED-BD37-8034367EA57A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="685800" y="0"/>
-          <a:ext cx="2257425" cy="2708910"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>676275</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="그림 32">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{618908DB-ECA8-4171-AF12-815BE44A0B43}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect l="2226" t="3766" r="2814" b="3447"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="685800" y="3143250"/>
-          <a:ext cx="2733675" cy="2800350"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>132819</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>142543</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="그림 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7485BFA2-B9CB-8304-8A27-9F61037517F2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="685800" y="6286500"/>
-          <a:ext cx="4247619" cy="2657143"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>94724</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>180638</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="그림 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47EA928A-1F81-702F-18DD-50B05274CB1E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="685800" y="9429750"/>
-          <a:ext cx="4209524" cy="2695238"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2046,38 +1798,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F31ECD23-1BD9-46B3-B60E-E26AB08DFCA7}">
-  <dimension ref="A1:A46"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A46">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD6F5ECB-A406-47E9-B55B-768631043F90}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:H78"/>
@@ -3361,7 +3081,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD266617-C88C-4574-ACBA-9832399CF3E6}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:L79"/>
